--- a/docs/タスク一覧.xlsx
+++ b/docs/タスク一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugur\Deploy\相続プラットフォーム\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26CF8621-F975-4FA8-A645-93F04E505853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D586797D-C6B1-481F-B398-2807907C6E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="案件タスク一覧" sheetId="6" r:id="rId1"/>
@@ -4319,30 +4319,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">相続人調査報告書作成
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>相関図作成</t>
-    </r>
-    <rPh sb="11" eb="14">
-      <t>ソウカンズ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>○○（権？システム？）で相関図の作成</t>
     <rPh sb="3" eb="4">
       <t>ケン</t>
@@ -6542,12 +6518,22 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>相関図作成</t>
+    <rPh sb="0" eb="3">
+      <t>ソウカンズ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6669,13 +6655,6 @@
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -7178,7 +7157,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H62"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.453125" style="3" customWidth="1"/>
@@ -7191,7 +7170,7 @@
     <col min="9" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="42" customHeight="1">
+    <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -7217,7 +7196,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="29" customHeight="1">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>98</v>
       </c>
@@ -7243,7 +7222,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="12" customFormat="1" ht="8.75" customHeight="1" thickBot="1">
+    <row r="4" spans="1:8" s="12" customFormat="1" ht="8.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7253,7 +7232,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:8" s="16" customFormat="1" ht="180.5" thickTop="1">
+    <row r="5" spans="1:8" s="16" customFormat="1" ht="180.5" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A61" si="0">ROW()-4</f>
         <v>1</v>
@@ -7278,7 +7257,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="6" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -7303,7 +7282,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="7" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -7330,7 +7309,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="16" customFormat="1" ht="27">
+    <row r="8" spans="1:8" s="16" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -7355,7 +7334,7 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" s="16" customFormat="1" ht="54">
+    <row r="9" spans="1:8" s="16" customFormat="1" ht="54" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7363,24 +7342,24 @@
       <c r="B9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>271</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>272</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" s="16" customFormat="1" ht="120">
+    <row r="10" spans="1:8" s="16" customFormat="1" ht="120" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -7407,7 +7386,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="16" customFormat="1" ht="185.25" customHeight="1">
+    <row r="11" spans="1:8" s="16" customFormat="1" ht="185.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -7434,7 +7413,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="16" customFormat="1" ht="169.5" customHeight="1">
+    <row r="12" spans="1:8" s="16" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -7461,7 +7440,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="16" customFormat="1" ht="169.5" customHeight="1">
+    <row r="13" spans="1:8" s="16" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -7488,7 +7467,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="16" customFormat="1" ht="270">
+    <row r="14" spans="1:8" s="16" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -7500,31 +7479,31 @@
         <v>21</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G14" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="16" customFormat="1" ht="69">
+    <row r="15" spans="1:8" s="16" customFormat="1" ht="69" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>277</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>278</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="9" t="s">
@@ -7533,33 +7512,33 @@
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="16" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C16" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>280</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>281</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="16" customFormat="1" ht="189">
+    <row r="17" spans="1:8" s="16" customFormat="1" ht="189" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -7571,45 +7550,45 @@
         <v>24</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="16" customFormat="1" ht="150">
+    <row r="18" spans="1:8" s="16" customFormat="1" ht="150" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="21" t="s">
         <v>287</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>288</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="19" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -7621,7 +7600,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>107</v>
@@ -7633,10 +7612,10 @@
         <v>27</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="16" customFormat="1" ht="27">
+    <row r="20" spans="1:8" s="16" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -7648,7 +7627,7 @@
         <v>28</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>107</v>
@@ -7661,7 +7640,7 @@
       </c>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" s="16" customFormat="1">
+    <row r="21" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -7684,7 +7663,7 @@
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" s="16" customFormat="1" ht="40.5">
+    <row r="22" spans="1:8" s="16" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -7693,21 +7672,21 @@
         <v>92</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>294</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>295</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="23" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -7716,10 +7695,10 @@
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>298</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>299</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>107</v>
@@ -7731,10 +7710,10 @@
         <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="24" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -7761,7 +7740,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="16" customFormat="1">
+    <row r="25" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -7786,7 +7765,7 @@
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" s="16" customFormat="1" ht="171.75" customHeight="1">
+    <row r="26" spans="1:8" s="16" customFormat="1" ht="171.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -7813,7 +7792,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="16" customFormat="1" ht="125.25" customHeight="1">
+    <row r="27" spans="1:8" s="16" customFormat="1" ht="125.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -7840,7 +7819,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="16" customFormat="1" ht="147" customHeight="1">
+    <row r="28" spans="1:8" s="16" customFormat="1" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -7867,7 +7846,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="16" customFormat="1" ht="189.75" customHeight="1">
+    <row r="29" spans="1:8" s="16" customFormat="1" ht="189.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -7879,7 +7858,7 @@
         <v>38</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>107</v>
@@ -7894,7 +7873,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="16" customFormat="1">
+    <row r="30" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -7919,7 +7898,7 @@
       </c>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" s="16" customFormat="1" ht="188.25" customHeight="1">
+    <row r="31" spans="1:8" s="16" customFormat="1" ht="188.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -7946,7 +7925,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="25" customFormat="1" ht="148.5" customHeight="1">
+    <row r="32" spans="1:8" s="25" customFormat="1" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -7973,7 +7952,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="25" customFormat="1" ht="136.5" customHeight="1">
+    <row r="33" spans="1:8" s="25" customFormat="1" ht="136.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -8000,7 +7979,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="16" customFormat="1">
+    <row r="34" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -8025,7 +8004,7 @@
       </c>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" s="25" customFormat="1" ht="154.5" customHeight="1">
+    <row r="35" spans="1:8" s="25" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -8052,7 +8031,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="16" customFormat="1" ht="130.5" customHeight="1">
+    <row r="36" spans="1:8" s="16" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -8079,7 +8058,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="16" customFormat="1" ht="150">
+    <row r="37" spans="1:8" s="16" customFormat="1" ht="150" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -8106,7 +8085,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="16" customFormat="1" ht="135">
+    <row r="38" spans="1:8" s="16" customFormat="1" ht="135" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -8133,19 +8112,19 @@
         <v>260</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="16" customFormat="1">
+    <row r="39" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B39" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>303</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>304</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>107</v>
@@ -8153,10 +8132,10 @@
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="16" customFormat="1" ht="147" customHeight="1">
+    <row r="40" spans="1:8" s="16" customFormat="1" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -8183,7 +8162,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="16" customFormat="1" ht="150">
+    <row r="41" spans="1:8" s="16" customFormat="1" ht="150" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -8195,7 +8174,7 @@
         <v>49</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>107</v>
@@ -8204,13 +8183,13 @@
         <v>40</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="42" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -8237,7 +8216,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="43" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -8264,7 +8243,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="16" customFormat="1" ht="116.25" customHeight="1">
+    <row r="44" spans="1:8" s="16" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -8291,7 +8270,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="25" customFormat="1" ht="153" customHeight="1">
+    <row r="45" spans="1:8" s="25" customFormat="1" ht="153" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -8318,7 +8297,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="25" customFormat="1" ht="141" customHeight="1">
+    <row r="46" spans="1:8" s="25" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -8345,7 +8324,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="25" customFormat="1" ht="136.5" customHeight="1">
+    <row r="47" spans="1:8" s="25" customFormat="1" ht="136.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -8372,7 +8351,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="25" customFormat="1" ht="123.75" customHeight="1">
+    <row r="48" spans="1:8" s="25" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -8399,7 +8378,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="16" customFormat="1" ht="150">
+    <row r="49" spans="1:8" s="16" customFormat="1" ht="150" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -8426,7 +8405,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="16" customFormat="1" ht="27">
+    <row r="50" spans="1:8" s="16" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -8449,7 +8428,7 @@
       </c>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="51" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -8461,13 +8440,13 @@
         <v>63</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G51" s="15" t="s">
         <v>64</v>
@@ -8476,7 +8455,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="52" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -8488,13 +8467,13 @@
         <v>65</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G52" s="15" t="s">
         <v>66</v>
@@ -8503,7 +8482,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="16" customFormat="1">
+    <row r="53" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -8528,7 +8507,7 @@
       </c>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" s="16" customFormat="1">
+    <row r="54" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -8553,7 +8532,7 @@
       </c>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" s="16" customFormat="1" ht="165">
+    <row r="55" spans="1:8" s="16" customFormat="1" ht="165" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -8580,7 +8559,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="56" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="56" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -8607,7 +8586,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="16" customFormat="1" ht="105">
+    <row r="57" spans="1:8" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -8634,7 +8613,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="16" customFormat="1">
+    <row r="58" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -8657,7 +8636,7 @@
       </c>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" s="16" customFormat="1" ht="180">
+    <row r="59" spans="1:8" s="16" customFormat="1" ht="180" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -8684,7 +8663,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="16" customFormat="1" ht="27">
+    <row r="60" spans="1:8" s="16" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -8709,7 +8688,7 @@
       </c>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" s="25" customFormat="1" ht="120">
+    <row r="61" spans="1:8" s="25" customFormat="1" ht="120" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -8736,7 +8715,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="23" customFormat="1">
+    <row r="62" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="H62" s="24"/>
     </row>
   </sheetData>
@@ -8766,7 +8745,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.453125" style="3" customWidth="1"/>
@@ -8780,7 +8759,7 @@
     <col min="10" max="16384" width="8.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="42" customHeight="1">
+    <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -8806,10 +8785,10 @@
         <v>97</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="29" customHeight="1">
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>98</v>
       </c>
@@ -8836,7 +8815,7 @@
       </c>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:9" s="12" customFormat="1" ht="8.75" customHeight="1" thickBot="1">
+    <row r="4" spans="1:9" s="12" customFormat="1" ht="8.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -8847,19 +8826,19 @@
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" s="25" customFormat="1" ht="175.5" customHeight="1" thickTop="1">
+    <row r="5" spans="1:9" s="25" customFormat="1" ht="175.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18">
         <f>ROW()-4</f>
         <v>1</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>323</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>324</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>108</v>
@@ -8868,10 +8847,10 @@
       <c r="G5" s="17"/>
       <c r="H5" s="22"/>
       <c r="I5" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="25" customFormat="1" ht="175.5" customHeight="1">
+    <row r="6" spans="1:9" s="25" customFormat="1" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="18">
         <f>ROW()-4</f>
         <v>2</v>
@@ -8880,7 +8859,7 @@
         <v>113</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>114</v>
@@ -8895,13 +8874,13 @@
         <v>117</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="25" customFormat="1" ht="130.5" customHeight="1">
+    <row r="7" spans="1:9" s="25" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="18">
         <f>ROW()-4</f>
         <v>3</v>
@@ -8910,7 +8889,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>131</v>
@@ -8928,10 +8907,10 @@
         <v>222</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="25" customFormat="1" ht="122.25" customHeight="1">
+    <row r="8" spans="1:9" s="25" customFormat="1" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18">
         <f>ROW()-4</f>
         <v>4</v>
@@ -8940,7 +8919,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>118</v>
@@ -8958,10 +8937,10 @@
         <v>223</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="25" customFormat="1" ht="122.25" customHeight="1">
+    <row r="9" spans="1:9" s="25" customFormat="1" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18">
         <f>ROW()-4</f>
         <v>5</v>
@@ -8970,10 +8949,10 @@
         <v>121</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>315</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>316</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>115</v>
@@ -8982,16 +8961,16 @@
         <v>119</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="25" customFormat="1" ht="116.25" customHeight="1">
+    <row r="10" spans="1:9" s="25" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="18">
         <f t="shared" ref="A10:A15" si="0">ROW()-4</f>
         <v>6</v>
@@ -9000,7 +8979,7 @@
         <v>121</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>122</v>
@@ -9018,10 +8997,10 @@
         <v>224</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="25" customFormat="1" ht="111.75" customHeight="1">
+    <row r="11" spans="1:9" s="25" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9048,10 +9027,10 @@
         <v>226</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="25" customFormat="1" ht="137.25" customHeight="1">
+    <row r="12" spans="1:9" s="25" customFormat="1" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9078,10 +9057,10 @@
         <v>227</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="25" customFormat="1" ht="139.5" customHeight="1">
+    <row r="13" spans="1:9" s="25" customFormat="1" ht="139.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9108,10 +9087,10 @@
         <v>228</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="25" customFormat="1" ht="137.25" customHeight="1">
+    <row r="14" spans="1:9" s="25" customFormat="1" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9138,25 +9117,25 @@
         <v>229</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="60">
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.35">
       <c r="A15" s="18">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -9183,24 +9162,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FF1C74-C245-4562-BD3A-69809ABADD45}">
   <dimension ref="B2:B5"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>109</v>
       </c>
